--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:11</t>
+    <t xml:space="preserve">2026-09-09 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:05</t>
+    <t xml:space="preserve">2026-09-17 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:02</t>
+    <t xml:space="preserve">2026-09-23 12:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:31</t>
+    <t xml:space="preserve">2026-10-02 14:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:12</t>
+    <t xml:space="preserve">2026-10-04 08:54</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:54</t>
+    <t xml:space="preserve">2026-10-05 10:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -609,7 +609,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>1320804.62</v>
+        <v>1320804.63</v>
       </c>
     </row>
     <row r="4">
@@ -643,7 +643,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1250699.12</v>
+        <v>1250699.13</v>
       </c>
     </row>
     <row r="6">
@@ -881,7 +881,7 @@
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1060622.12</v>
+        <v>1060622.13</v>
       </c>
     </row>
     <row r="20">
@@ -932,7 +932,7 @@
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1039639.62</v>
+        <v>1039639.63</v>
       </c>
     </row>
     <row r="23">
@@ -1000,7 +1000,7 @@
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1026519.12</v>
+        <v>1026519.13</v>
       </c>
     </row>
     <row r="27">
